--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/165.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/165.xlsx
@@ -426,13 +426,13 @@
         <v>-2.355261336636374</v>
       </c>
       <c r="E2">
-        <v>-7.125266105440419</v>
+        <v>-7.705218714654746</v>
       </c>
       <c r="F2">
-        <v>-4.439245520243843</v>
+        <v>-4.110431746962559</v>
       </c>
       <c r="G2">
-        <v>-12.29887315124761</v>
+        <v>-11.41801974688603</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.558064327200121</v>
       </c>
       <c r="E3">
-        <v>-7.204274391452243</v>
+        <v>-7.583470690958528</v>
       </c>
       <c r="F3">
-        <v>-4.176796151496091</v>
+        <v>-4.544127236346778</v>
       </c>
       <c r="G3">
-        <v>-12.37807464272914</v>
+        <v>-12.01444763124113</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.684705357028401</v>
       </c>
       <c r="E4">
-        <v>-8.263792398078861</v>
+        <v>-10.04498160798985</v>
       </c>
       <c r="F4">
-        <v>-4.342150886127124</v>
+        <v>-4.310407084758055</v>
       </c>
       <c r="G4">
-        <v>-12.42080385400451</v>
+        <v>-10.54837916026596</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.684613780262047</v>
       </c>
       <c r="E5">
-        <v>-8.980622662649033</v>
+        <v>-7.720257776834219</v>
       </c>
       <c r="F5">
-        <v>-4.470466698660816</v>
+        <v>-4.269465119432115</v>
       </c>
       <c r="G5">
-        <v>-11.92351356636843</v>
+        <v>-10.19792149893317</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.544059842837522</v>
       </c>
       <c r="E6">
-        <v>-10.06881496669222</v>
+        <v>-9.517704208432745</v>
       </c>
       <c r="F6">
-        <v>-4.181304962237347</v>
+        <v>-4.232371559480692</v>
       </c>
       <c r="G6">
-        <v>-11.02988807731634</v>
+        <v>-10.52516230439905</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.24955353666621</v>
       </c>
       <c r="E7">
-        <v>-9.580029596200312</v>
+        <v>-10.67484705771672</v>
       </c>
       <c r="F7">
-        <v>-4.308680053457269</v>
+        <v>-3.995560805797989</v>
       </c>
       <c r="G7">
-        <v>-10.91112556664052</v>
+        <v>-10.9770120439631</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.80561284820019</v>
       </c>
       <c r="E8">
-        <v>-11.10341730932864</v>
+        <v>-11.97538856492759</v>
       </c>
       <c r="F8">
-        <v>-4.475876638067957</v>
+        <v>-4.237304803407286</v>
       </c>
       <c r="G8">
-        <v>-11.01589440132184</v>
+        <v>-10.62750450920008</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.223769620692082</v>
       </c>
       <c r="E9">
-        <v>-11.62009807970779</v>
+        <v>-10.86387009127089</v>
       </c>
       <c r="F9">
-        <v>-4.280779906344972</v>
+        <v>-4.154379586116003</v>
       </c>
       <c r="G9">
-        <v>-10.05348901814585</v>
+        <v>-8.737262459369175</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.5301019769506649</v>
       </c>
       <c r="E10">
-        <v>-12.39653664764093</v>
+        <v>-11.6110094323744</v>
       </c>
       <c r="F10">
-        <v>-4.266666711079533</v>
+        <v>-4.274778452778414</v>
       </c>
       <c r="G10">
-        <v>-10.74570422713422</v>
+        <v>-8.863970279339242</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.2419259701455114</v>
       </c>
       <c r="E11">
-        <v>-12.40302595089392</v>
+        <v>-12.32228778781117</v>
       </c>
       <c r="F11">
-        <v>-4.177823976635211</v>
+        <v>-3.770724452541924</v>
       </c>
       <c r="G11">
-        <v>-10.13754045884241</v>
+        <v>-9.748359346336764</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.056512893496593</v>
       </c>
       <c r="E12">
-        <v>-12.63546799323363</v>
+        <v>-12.34692268641289</v>
       </c>
       <c r="F12">
-        <v>-4.285383739441154</v>
+        <v>-3.975910974652174</v>
       </c>
       <c r="G12">
-        <v>-8.74533025884838</v>
+        <v>-9.094761651063992</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.872645077479338</v>
       </c>
       <c r="E13">
-        <v>-13.80098399095779</v>
+        <v>-13.670043165026</v>
       </c>
       <c r="F13">
-        <v>-3.908848947662891</v>
+        <v>-4.082888725534193</v>
       </c>
       <c r="G13">
-        <v>-9.164872384494677</v>
+        <v>-8.483932893613066</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.646745300325605</v>
       </c>
       <c r="E14">
-        <v>-14.73680220159089</v>
+        <v>-16.32941216840046</v>
       </c>
       <c r="F14">
-        <v>-3.797096323445821</v>
+        <v>-3.900329401690784</v>
       </c>
       <c r="G14">
-        <v>-8.75763886716339</v>
+        <v>-7.901995267083358</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.343329667875239</v>
       </c>
       <c r="E15">
-        <v>-15.21961904334068</v>
+        <v>-14.97735021240433</v>
       </c>
       <c r="F15">
-        <v>-4.150396565738673</v>
+        <v>-3.813108382103872</v>
       </c>
       <c r="G15">
-        <v>-8.32547363137585</v>
+        <v>-7.087839423701475</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.935214689351511</v>
       </c>
       <c r="E16">
-        <v>-16.83467212733227</v>
+        <v>-15.81411258259364</v>
       </c>
       <c r="F16">
-        <v>-3.547803591590583</v>
+        <v>-3.40237821219944</v>
       </c>
       <c r="G16">
-        <v>-7.459292564844319</v>
+        <v>-7.186301669130478</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.406606744206513</v>
       </c>
       <c r="E17">
-        <v>-16.98274869890908</v>
+        <v>-17.18102793333493</v>
       </c>
       <c r="F17">
-        <v>-3.834270652398932</v>
+        <v>-4.080883753845247</v>
       </c>
       <c r="G17">
-        <v>-7.509493677401827</v>
+        <v>-6.094953847745416</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.758472365162537</v>
       </c>
       <c r="E18">
-        <v>-17.4498109795862</v>
+        <v>-16.91524726535075</v>
       </c>
       <c r="F18">
-        <v>-3.744523621876894</v>
+        <v>-3.779767413319083</v>
       </c>
       <c r="G18">
-        <v>-6.514886617765349</v>
+        <v>-5.652827180430211</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.999476695526414</v>
       </c>
       <c r="E19">
-        <v>-19.44648762515218</v>
+        <v>-18.53640020383067</v>
       </c>
       <c r="F19">
-        <v>-3.283307282947125</v>
+        <v>-3.451903863587062</v>
       </c>
       <c r="G19">
-        <v>-6.042597570041843</v>
+        <v>-5.589791082816948</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.142768897854936</v>
       </c>
       <c r="E20">
-        <v>-19.10365044345348</v>
+        <v>-18.69839730450706</v>
       </c>
       <c r="F20">
-        <v>-3.15637087826578</v>
+        <v>-3.055225916270325</v>
       </c>
       <c r="G20">
-        <v>-5.817334809367674</v>
+        <v>-5.754017315383574</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.206600521752453</v>
       </c>
       <c r="E21">
-        <v>-19.62737299091457</v>
+        <v>-19.64164221251274</v>
       </c>
       <c r="F21">
-        <v>-2.876114320204827</v>
+        <v>-3.142350329796395</v>
       </c>
       <c r="G21">
-        <v>-6.621830480865966</v>
+        <v>-6.188655528688948</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.206315313160315</v>
       </c>
       <c r="E22">
-        <v>-20.55139905523169</v>
+        <v>-20.05551756596976</v>
       </c>
       <c r="F22">
-        <v>-2.910956642197453</v>
+        <v>-2.704450893059641</v>
       </c>
       <c r="G22">
-        <v>-6.098986092212249</v>
+        <v>-6.467691480557499</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.155995566095553</v>
       </c>
       <c r="E23">
-        <v>-19.79992596450284</v>
+        <v>-19.56307771695366</v>
       </c>
       <c r="F23">
-        <v>-2.67951781897992</v>
+        <v>-2.636111607249556</v>
       </c>
       <c r="G23">
-        <v>-6.702872635667324</v>
+        <v>-5.556937228885221</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.067493207997606</v>
       </c>
       <c r="E24">
-        <v>-19.64477591652604</v>
+        <v>-19.21926691334331</v>
       </c>
       <c r="F24">
-        <v>-2.716368280073323</v>
+        <v>-2.886075830412941</v>
       </c>
       <c r="G24">
-        <v>-6.431738956001014</v>
+        <v>-5.530151604926977</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.94532143317873</v>
       </c>
       <c r="E25">
-        <v>-20.2191358603409</v>
+        <v>-21.63534817912969</v>
       </c>
       <c r="F25">
-        <v>-2.947528371049738</v>
+        <v>-2.577637225586743</v>
       </c>
       <c r="G25">
-        <v>-6.537967741265148</v>
+        <v>-6.639141323490814</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.794188849420708</v>
       </c>
       <c r="E26">
-        <v>-20.16309599449598</v>
+        <v>-20.68800953062108</v>
       </c>
       <c r="F26">
-        <v>-2.909528139461727</v>
+        <v>-2.424419221238681</v>
       </c>
       <c r="G26">
-        <v>-7.593320001001713</v>
+        <v>-6.3934657390215</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.619502442584687</v>
       </c>
       <c r="E27">
-        <v>-20.55763929241425</v>
+        <v>-20.83533890398662</v>
       </c>
       <c r="F27">
-        <v>-2.838307300738499</v>
+        <v>-2.203429689651218</v>
       </c>
       <c r="G27">
-        <v>-7.101127953496109</v>
+        <v>-6.959678274239669</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.424733263857918</v>
       </c>
       <c r="E28">
-        <v>-19.94488241748837</v>
+        <v>-19.43819598924414</v>
       </c>
       <c r="F28">
-        <v>-2.913203129038504</v>
+        <v>-2.499557356543748</v>
       </c>
       <c r="G28">
-        <v>-7.122034048576606</v>
+        <v>-6.838869846420584</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.2198760173265</v>
       </c>
       <c r="E29">
-        <v>-20.83783862163886</v>
+        <v>-19.3692182731593</v>
       </c>
       <c r="F29">
-        <v>-2.937880434612881</v>
+        <v>-2.42684308314226</v>
       </c>
       <c r="G29">
-        <v>-7.599752390984517</v>
+        <v>-7.292143120566517</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.016001073450231</v>
       </c>
       <c r="E30">
-        <v>-20.10945621987512</v>
+        <v>-18.89210278018516</v>
       </c>
       <c r="F30">
-        <v>-2.768427069072691</v>
+        <v>-2.556770316444913</v>
       </c>
       <c r="G30">
-        <v>-7.263933962026387</v>
+        <v>-7.17048719308938</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.821146148970246</v>
       </c>
       <c r="E31">
-        <v>-20.42405383766199</v>
+        <v>-19.03633920580347</v>
       </c>
       <c r="F31">
-        <v>-2.781008028864942</v>
+        <v>-2.834586383690174</v>
       </c>
       <c r="G31">
-        <v>-7.775787339489723</v>
+        <v>-7.65820338302589</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.646374809184483</v>
       </c>
       <c r="E32">
-        <v>-19.47275277439667</v>
+        <v>-19.00680902679945</v>
       </c>
       <c r="F32">
-        <v>-3.067057783164573</v>
+        <v>-2.565843367634466</v>
       </c>
       <c r="G32">
-        <v>-7.763591289723048</v>
+        <v>-6.904733149924385</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.498037302060847</v>
       </c>
       <c r="E33">
-        <v>-18.63232234026114</v>
+        <v>-18.80991097694594</v>
       </c>
       <c r="F33">
-        <v>-2.896287566155695</v>
+        <v>-2.70705925670237</v>
       </c>
       <c r="G33">
-        <v>-7.291643228190087</v>
+        <v>-7.763826338456337</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.375137938169599</v>
       </c>
       <c r="E34">
-        <v>-19.19012618310395</v>
+        <v>-17.88973864400935</v>
       </c>
       <c r="F34">
-        <v>-2.77482048985332</v>
+        <v>-2.3898738441052</v>
       </c>
       <c r="G34">
-        <v>-7.848175728251427</v>
+        <v>-6.958003138196798</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.277291495174131</v>
       </c>
       <c r="E35">
-        <v>-18.05563023233234</v>
+        <v>-18.1625882599195</v>
       </c>
       <c r="F35">
-        <v>-2.756378234468028</v>
+        <v>-2.297267432552836</v>
       </c>
       <c r="G35">
-        <v>-7.198434818531907</v>
+        <v>-6.923825066049361</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.198830304799666</v>
       </c>
       <c r="E36">
-        <v>-17.67784228824244</v>
+        <v>-18.13609215850062</v>
       </c>
       <c r="F36">
-        <v>-2.824835506368813</v>
+        <v>-1.932357042193898</v>
       </c>
       <c r="G36">
-        <v>-6.486554969040267</v>
+        <v>-7.2032814572014</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.128908060273238</v>
       </c>
       <c r="E37">
-        <v>-17.19401559678893</v>
+        <v>-16.70701897353005</v>
       </c>
       <c r="F37">
-        <v>-2.725553774382872</v>
+        <v>-2.095274453421069</v>
       </c>
       <c r="G37">
-        <v>-6.446033891639587</v>
+        <v>-6.441961920626284</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.061166647025293</v>
       </c>
       <c r="E38">
-        <v>-16.43849405029722</v>
+        <v>-16.46561055265515</v>
       </c>
       <c r="F38">
-        <v>-2.721077429612882</v>
+        <v>-2.468418530834377</v>
       </c>
       <c r="G38">
-        <v>-6.469303716235124</v>
+        <v>-7.10802713039995</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.990670026008763</v>
       </c>
       <c r="E39">
-        <v>-16.55881560468102</v>
+        <v>-16.2579392631374</v>
       </c>
       <c r="F39">
-        <v>-2.469813775745879</v>
+        <v>-1.950690813723983</v>
       </c>
       <c r="G39">
-        <v>-6.409217314697352</v>
+        <v>-6.523073596883966</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.914399387184242</v>
       </c>
       <c r="E40">
-        <v>-16.08266920514452</v>
+        <v>-15.01533052390666</v>
       </c>
       <c r="F40">
-        <v>-2.663945238713405</v>
+        <v>-2.277489321227871</v>
       </c>
       <c r="G40">
-        <v>-6.596173752936614</v>
+        <v>-6.104885484363231</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.838179501706845</v>
       </c>
       <c r="E41">
-        <v>-15.64150073884327</v>
+        <v>-15.63588543107376</v>
       </c>
       <c r="F41">
-        <v>-2.48337425764683</v>
+        <v>-1.850123112534705</v>
       </c>
       <c r="G41">
-        <v>-7.386238756429222</v>
+        <v>-6.520845599736037</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.769832063963973</v>
       </c>
       <c r="E42">
-        <v>-16.29735510090016</v>
+        <v>-16.40293647238899</v>
       </c>
       <c r="F42">
-        <v>-2.590134248965476</v>
+        <v>-2.13610872674476</v>
       </c>
       <c r="G42">
-        <v>-6.669002444255041</v>
+        <v>-7.250228303493804</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.716690939477123</v>
       </c>
       <c r="E43">
-        <v>-15.55220828836003</v>
+        <v>-14.63700821988385</v>
       </c>
       <c r="F43">
-        <v>-2.422101467631435</v>
+        <v>-2.291742674466826</v>
       </c>
       <c r="G43">
-        <v>-7.071624371650124</v>
+        <v>-7.535699955890698</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.689814177877044</v>
       </c>
       <c r="E44">
-        <v>-14.61447906169569</v>
+        <v>-13.99158293346663</v>
       </c>
       <c r="F44">
-        <v>-2.083238288463729</v>
+        <v>-2.246610223288632</v>
       </c>
       <c r="G44">
-        <v>-6.935332522343868</v>
+        <v>-7.006118607064565</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.696028359755869</v>
       </c>
       <c r="E45">
-        <v>-13.90630723942819</v>
+        <v>-13.11062718543646</v>
       </c>
       <c r="F45">
-        <v>-2.556954818184062</v>
+        <v>-2.21670827189922</v>
       </c>
       <c r="G45">
-        <v>-7.109679092624046</v>
+        <v>-6.76666684820908</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.735403919516533</v>
       </c>
       <c r="E46">
-        <v>-14.5889746960845</v>
+        <v>-13.15246122831932</v>
       </c>
       <c r="F46">
-        <v>-2.943090035221719</v>
+        <v>-2.263846486619317</v>
       </c>
       <c r="G46">
-        <v>-7.734259856245106</v>
+        <v>-6.535160398647846</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.805753339185739</v>
       </c>
       <c r="E47">
-        <v>-13.36491911486318</v>
+        <v>-13.18180121141502</v>
       </c>
       <c r="F47">
-        <v>-2.412528757225561</v>
+        <v>-2.802920183910962</v>
       </c>
       <c r="G47">
-        <v>-7.507331891164683</v>
+        <v>-6.630931170553422</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.896915647699316</v>
       </c>
       <c r="E48">
-        <v>-13.61983597370296</v>
+        <v>-12.57926057385043</v>
       </c>
       <c r="F48">
-        <v>-2.464598632166337</v>
+        <v>-2.817835526222571</v>
       </c>
       <c r="G48">
-        <v>-7.283198026519406</v>
+        <v>-7.501392772467231</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.993171426807785</v>
       </c>
       <c r="E49">
-        <v>-12.80880439282523</v>
+        <v>-11.56132754403625</v>
       </c>
       <c r="F49">
-        <v>-2.599510579837835</v>
+        <v>-2.251211680825941</v>
       </c>
       <c r="G49">
-        <v>-7.442428645867271</v>
+        <v>-6.896135663158898</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.080501928036214</v>
       </c>
       <c r="E50">
-        <v>-12.81754887613404</v>
+        <v>-11.25759373539378</v>
       </c>
       <c r="F50">
-        <v>-2.500705543332441</v>
+        <v>-2.705994214474237</v>
       </c>
       <c r="G50">
-        <v>-7.680420454139938</v>
+        <v>-7.645682899796365</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.143091108032134</v>
       </c>
       <c r="E51">
-        <v>-11.83959774333358</v>
+        <v>-12.72752734133556</v>
       </c>
       <c r="F51">
-        <v>-2.479199608853731</v>
+        <v>-2.767559990083988</v>
       </c>
       <c r="G51">
-        <v>-7.60246041723564</v>
+        <v>-7.357281414597217</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.166074223908815</v>
       </c>
       <c r="E52">
-        <v>-12.01429268512748</v>
+        <v>-12.0556285958695</v>
       </c>
       <c r="F52">
-        <v>-2.787440250440499</v>
+        <v>-2.218649895351549</v>
       </c>
       <c r="G52">
-        <v>-7.948899076283753</v>
+        <v>-7.533663970384047</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.140498771840255</v>
       </c>
       <c r="E53">
-        <v>-11.08346032437683</v>
+        <v>-10.31052679532563</v>
       </c>
       <c r="F53">
-        <v>-2.841136591356431</v>
+        <v>-2.210159647938878</v>
       </c>
       <c r="G53">
-        <v>-8.152150019667307</v>
+        <v>-7.281105761738587</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.060272800583325</v>
       </c>
       <c r="E54">
-        <v>-10.26970713062049</v>
+        <v>-11.53179736503223</v>
       </c>
       <c r="F54">
-        <v>-2.900375111123444</v>
+        <v>-2.625540370263998</v>
       </c>
       <c r="G54">
-        <v>-7.699893083001931</v>
+        <v>-8.018384116607516</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.924683425232707</v>
       </c>
       <c r="E55">
-        <v>-11.14158328826528</v>
+        <v>-10.49096384216126</v>
       </c>
       <c r="F55">
-        <v>-2.543306440604804</v>
+        <v>-2.785787653317738</v>
       </c>
       <c r="G55">
-        <v>-8.258501295116394</v>
+        <v>-7.806529065367395</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.740784020825805</v>
       </c>
       <c r="E56">
-        <v>-10.38748368261198</v>
+        <v>-10.46617950391728</v>
       </c>
       <c r="F56">
-        <v>-2.901912097714378</v>
+        <v>-2.747148396392847</v>
       </c>
       <c r="G56">
-        <v>-8.382554057563965</v>
+        <v>-7.078113040907096</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.518635068767935</v>
       </c>
       <c r="E57">
-        <v>-9.926453329313087</v>
+        <v>-11.27647294353176</v>
       </c>
       <c r="F57">
-        <v>-2.79556941290445</v>
+        <v>-2.838808543660736</v>
       </c>
       <c r="G57">
-        <v>-8.451261119685999</v>
+        <v>-7.405112176548607</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.270087345115327</v>
       </c>
       <c r="E58">
-        <v>-10.38470772804528</v>
+        <v>-9.493327432849455</v>
       </c>
       <c r="F58">
-        <v>-3.149393861855312</v>
+        <v>-3.004921873425264</v>
       </c>
       <c r="G58">
-        <v>-8.871677229354665</v>
+        <v>-8.078076563226114</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.009005297783445</v>
       </c>
       <c r="E59">
-        <v>-9.747121230135333</v>
+        <v>-8.510576117600865</v>
       </c>
       <c r="F59">
-        <v>-2.945135391411509</v>
+        <v>-3.191081752667424</v>
       </c>
       <c r="G59">
-        <v>-7.564283206076766</v>
+        <v>-7.759108811062875</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.746883672136105</v>
       </c>
       <c r="E60">
-        <v>-10.60715089977606</v>
+        <v>-9.368151354329431</v>
       </c>
       <c r="F60">
-        <v>-3.221739131778501</v>
+        <v>-2.835919864070974</v>
       </c>
       <c r="G60">
-        <v>-8.356596069990539</v>
+        <v>-7.97162266086531</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.493775346320531</v>
       </c>
       <c r="E61">
-        <v>-9.184286252669999</v>
+        <v>-9.278963058748364</v>
       </c>
       <c r="F61">
-        <v>-3.004558412917671</v>
+        <v>-2.71526522890322</v>
       </c>
       <c r="G61">
-        <v>-8.173416964211585</v>
+        <v>-8.125645792079903</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.259333768314477</v>
       </c>
       <c r="E62">
-        <v>-9.504404080272217</v>
+        <v>-10.24998109784308</v>
       </c>
       <c r="F62">
-        <v>-2.798319518226611</v>
+        <v>-2.8192283955752</v>
       </c>
       <c r="G62">
-        <v>-8.963981860080624</v>
+        <v>-7.91297965718266</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.04913473171158</v>
       </c>
       <c r="E63">
-        <v>-9.171755965090776</v>
+        <v>-8.984979054644413</v>
       </c>
       <c r="F63">
-        <v>-2.979065498796841</v>
+        <v>-3.017309621095831</v>
       </c>
       <c r="G63">
-        <v>-8.022856663631071</v>
+        <v>-8.149402266869712</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.8663667981496628</v>
       </c>
       <c r="E64">
-        <v>-8.533857002474299</v>
+        <v>-7.528956920854193</v>
       </c>
       <c r="F64">
-        <v>-2.814196961881849</v>
+        <v>-2.780807690066639</v>
       </c>
       <c r="G64">
-        <v>-9.593912465293146</v>
+        <v>-7.349014982385657</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.7147858752624218</v>
       </c>
       <c r="E65">
-        <v>-8.61502989906179</v>
+        <v>-7.952242443299157</v>
       </c>
       <c r="F65">
-        <v>-2.739749322355914</v>
+        <v>-2.868259138864247</v>
       </c>
       <c r="G65">
-        <v>-8.776644709104346</v>
+        <v>-8.859474558496911</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.5955241454351663</v>
       </c>
       <c r="E66">
-        <v>-10.34898259659877</v>
+        <v>-8.963409932945877</v>
       </c>
       <c r="F66">
-        <v>-3.058018781652202</v>
+        <v>-3.558216457984597</v>
       </c>
       <c r="G66">
-        <v>-8.6673801535807</v>
+        <v>-9.145174638536014</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.5095883426358813</v>
       </c>
       <c r="E67">
-        <v>-9.02714367612983</v>
+        <v>-7.866984863156746</v>
       </c>
       <c r="F67">
-        <v>-3.164138163928053</v>
+        <v>-3.149747028274455</v>
       </c>
       <c r="G67">
-        <v>-9.053770476196737</v>
+        <v>-8.524857857569536</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.4581027178878273</v>
       </c>
       <c r="E68">
-        <v>-8.494862312794249</v>
+        <v>-8.25485319038772</v>
       </c>
       <c r="F68">
-        <v>-3.295451139906715</v>
+        <v>-3.021190492441615</v>
       </c>
       <c r="G68">
-        <v>-9.151765934704702</v>
+        <v>-8.080695204747679</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.4388482855928163</v>
       </c>
       <c r="E69">
-        <v>-8.920104136010526</v>
+        <v>-8.10278703321015</v>
       </c>
       <c r="F69">
-        <v>-3.098560069381536</v>
+        <v>-3.353682422711508</v>
       </c>
       <c r="G69">
-        <v>-9.384242374108943</v>
+        <v>-8.279215378555614</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.4476440263604106</v>
       </c>
       <c r="E70">
-        <v>-8.282236872712103</v>
+        <v>-7.55601908152403</v>
       </c>
       <c r="F70">
-        <v>-3.276479926745666</v>
+        <v>-2.769921295603908</v>
       </c>
       <c r="G70">
-        <v>-9.62232356711117</v>
+        <v>-8.245063790772493</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.4789619307821675</v>
       </c>
       <c r="E71">
-        <v>-9.165099108299501</v>
+        <v>-9.154688146555866</v>
       </c>
       <c r="F71">
-        <v>-3.205095966313148</v>
+        <v>-2.749295901614182</v>
       </c>
       <c r="G71">
-        <v>-9.769450831967461</v>
+        <v>-9.321941217605399</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.5240229699014626</v>
       </c>
       <c r="E72">
-        <v>-9.790268530480416</v>
+        <v>-8.931212482751341</v>
       </c>
       <c r="F72">
-        <v>-3.174176483873066</v>
+        <v>-3.265172266509428</v>
       </c>
       <c r="G72">
-        <v>-9.700230635286839</v>
+        <v>-8.72679120382846</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.5735071998561893</v>
       </c>
       <c r="E73">
-        <v>-8.664254411525166</v>
+        <v>-9.448558938809626</v>
       </c>
       <c r="F73">
-        <v>-3.19376771790001</v>
+        <v>-2.344224312945616</v>
       </c>
       <c r="G73">
-        <v>-9.449675306692638</v>
+        <v>-8.928959598820674</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.6195068896694476</v>
       </c>
       <c r="E74">
-        <v>-9.367752848616757</v>
+        <v>-9.726136281583788</v>
       </c>
       <c r="F74">
-        <v>-3.047556820374809</v>
+        <v>-2.957646668143481</v>
       </c>
       <c r="G74">
-        <v>-9.4218700347083</v>
+        <v>-8.503150610468534</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.654799387018401</v>
       </c>
       <c r="E75">
-        <v>-9.692054986202061</v>
+        <v>-9.529804290981239</v>
       </c>
       <c r="F75">
-        <v>-3.312441928820507</v>
+        <v>-2.930266768424406</v>
       </c>
       <c r="G75">
-        <v>-9.458895176019508</v>
+        <v>-7.922729213795814</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.6743176780720079</v>
       </c>
       <c r="E76">
-        <v>-10.73791964369555</v>
+        <v>-10.67725167741479</v>
       </c>
       <c r="F76">
-        <v>-3.268140923247919</v>
+        <v>-3.316553229376988</v>
       </c>
       <c r="G76">
-        <v>-9.620727884161241</v>
+        <v>-9.627607197791846</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.6753187639115018</v>
       </c>
       <c r="E77">
-        <v>-10.80604147819294</v>
+        <v>-11.33702316948832</v>
       </c>
       <c r="F77">
-        <v>-3.449618575951083</v>
+        <v>-3.056132587906914</v>
       </c>
       <c r="G77">
-        <v>-10.10011805206648</v>
+        <v>-8.694298199360514</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.6567255230444625</v>
       </c>
       <c r="E78">
-        <v>-11.90790524526528</v>
+        <v>-11.5521483272227</v>
       </c>
       <c r="F78">
-        <v>-3.34615665220134</v>
+        <v>-3.215049557991685</v>
       </c>
       <c r="G78">
-        <v>-9.725228564653875</v>
+        <v>-9.375780619710566</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.6194189388094364</v>
       </c>
       <c r="E79">
-        <v>-11.51618771512779</v>
+        <v>-10.29257592435923</v>
       </c>
       <c r="F79">
-        <v>-3.447155913252575</v>
+        <v>-3.084323345054694</v>
       </c>
       <c r="G79">
-        <v>-10.05122129445145</v>
+        <v>-8.634330977462156</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5655501911736414</v>
       </c>
       <c r="E80">
-        <v>-12.63444908658191</v>
+        <v>-10.80530333692969</v>
       </c>
       <c r="F80">
-        <v>-3.425931878426813</v>
+        <v>-2.883309888031626</v>
       </c>
       <c r="G80">
-        <v>-10.53722593234416</v>
+        <v>-9.231761957115651</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.4981189616981516</v>
       </c>
       <c r="E81">
-        <v>-12.79932176825317</v>
+        <v>-12.69474118952003</v>
       </c>
       <c r="F81">
-        <v>-3.85495068424274</v>
+        <v>-3.127600484752949</v>
       </c>
       <c r="G81">
-        <v>-10.16666663849691</v>
+        <v>-8.715369821717974</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.4214383630932638</v>
       </c>
       <c r="E82">
-        <v>-13.3452111959818</v>
+        <v>-13.07712553472772</v>
       </c>
       <c r="F82">
-        <v>-3.613171053250346</v>
+        <v>-3.398848131713926</v>
       </c>
       <c r="G82">
-        <v>-9.675113526280388</v>
+        <v>-9.108454067414417</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.3396865216383375</v>
       </c>
       <c r="E83">
-        <v>-14.26103166539702</v>
+        <v>-14.31349403677588</v>
       </c>
       <c r="F83">
-        <v>-3.57887748535742</v>
+        <v>-3.934086885131334</v>
       </c>
       <c r="G83">
-        <v>-10.46996888916832</v>
+        <v>-8.798318850749954</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.2560934321917901</v>
       </c>
       <c r="E84">
-        <v>-15.77838292267312</v>
+        <v>-14.80351568067189</v>
       </c>
       <c r="F84">
-        <v>-3.423379736344083</v>
+        <v>-3.510733787227892</v>
       </c>
       <c r="G84">
-        <v>-10.04321970588303</v>
+        <v>-8.587827744272014</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.1729199962233515</v>
       </c>
       <c r="E85">
-        <v>-17.11421029935175</v>
+        <v>-15.43791866135444</v>
       </c>
       <c r="F85">
-        <v>-3.377909163952943</v>
+        <v>-3.419851239564483</v>
       </c>
       <c r="G85">
-        <v>-10.64890056502039</v>
+        <v>-9.218195341495719</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.08899109406169452</v>
       </c>
       <c r="E86">
-        <v>-17.11513410804932</v>
+        <v>-17.01040861814793</v>
       </c>
       <c r="F86">
-        <v>-3.858538569994168</v>
+        <v>-3.736183034673232</v>
       </c>
       <c r="G86">
-        <v>-10.05634932949178</v>
+        <v>-8.692662789864114</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.0002616924215613653</v>
       </c>
       <c r="E87">
-        <v>-17.8719960828473</v>
+        <v>-18.46240493854533</v>
       </c>
       <c r="F87">
-        <v>-4.143881991455513</v>
+        <v>-3.584672265302013</v>
       </c>
       <c r="G87">
-        <v>-10.31809761255426</v>
+        <v>-8.818675395270933</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.09869770041079454</v>
       </c>
       <c r="E88">
-        <v>-20.59815102088687</v>
+        <v>-20.14400394807964</v>
       </c>
       <c r="F88">
-        <v>-3.781222839055372</v>
+        <v>-3.756752207102959</v>
       </c>
       <c r="G88">
-        <v>-10.26944252476359</v>
+        <v>-8.192644612703672</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.2174378968965264</v>
       </c>
       <c r="E89">
-        <v>-21.77473008061177</v>
+        <v>-20.39451007323595</v>
       </c>
       <c r="F89">
-        <v>-3.775808148530484</v>
+        <v>-3.869725076727875</v>
       </c>
       <c r="G89">
-        <v>-10.46457932103039</v>
+        <v>-9.019301076041845</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.36536285932083</v>
       </c>
       <c r="E90">
-        <v>-22.80733989468481</v>
+        <v>-22.31702389997831</v>
       </c>
       <c r="F90">
-        <v>-3.643470514824533</v>
+        <v>-3.67303751241283</v>
       </c>
       <c r="G90">
-        <v>-9.855121129432719</v>
+        <v>-9.200222389763015</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.5489966644485483</v>
       </c>
       <c r="E91">
-        <v>-24.23340164444028</v>
+        <v>-24.70429048565388</v>
       </c>
       <c r="F91">
-        <v>-3.677599377302254</v>
+        <v>-3.845500711045313</v>
       </c>
       <c r="G91">
-        <v>-9.865347404603529</v>
+        <v>-8.40287749662955</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.7754934860046767</v>
       </c>
       <c r="E92">
-        <v>-26.35491020450171</v>
+        <v>-25.60991736007784</v>
       </c>
       <c r="F92">
-        <v>-3.634288187926816</v>
+        <v>-3.328860999898826</v>
       </c>
       <c r="G92">
-        <v>-10.08011242537267</v>
+        <v>-8.685204130764136</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.046630176417227</v>
       </c>
       <c r="E93">
-        <v>-28.41835467083678</v>
+        <v>-28.0870967971757</v>
       </c>
       <c r="F93">
-        <v>-3.742939915961454</v>
+        <v>-3.738904633288914</v>
       </c>
       <c r="G93">
-        <v>-10.62253538034564</v>
+        <v>-8.926423720937592</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.357739580347003</v>
       </c>
       <c r="E94">
-        <v>-30.54957680764466</v>
+        <v>-29.07960244543681</v>
       </c>
       <c r="F94">
-        <v>-3.765076957247467</v>
+        <v>-3.933479533912763</v>
       </c>
       <c r="G94">
-        <v>-10.00294029830672</v>
+        <v>-8.37980299422083</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.7022731679745</v>
       </c>
       <c r="E95">
-        <v>-33.18942355957205</v>
+        <v>-32.06349774585995</v>
       </c>
       <c r="F95">
-        <v>-3.644065988248739</v>
+        <v>-3.973226593125504</v>
       </c>
       <c r="G95">
-        <v>-10.45110209014002</v>
+        <v>-9.601258565844788</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.070430127810724</v>
       </c>
       <c r="E96">
-        <v>-34.95814361630292</v>
+        <v>-35.49111557192467</v>
       </c>
       <c r="F96">
-        <v>-3.358176188246567</v>
+        <v>-3.966316092363484</v>
       </c>
       <c r="G96">
-        <v>-9.968878095253157</v>
+        <v>-9.670832990898111</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.445394219355523</v>
       </c>
       <c r="E97">
-        <v>-37.28861181673728</v>
+        <v>-36.81002909818466</v>
       </c>
       <c r="F97">
-        <v>-3.594672576305056</v>
+        <v>-3.429473044853736</v>
       </c>
       <c r="G97">
-        <v>-10.67763610030126</v>
+        <v>-10.0697967654723</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.824252259536268</v>
       </c>
       <c r="E98">
-        <v>-40.13437507450445</v>
+        <v>-38.64844010565657</v>
       </c>
       <c r="F98">
-        <v>-3.202646765114921</v>
+        <v>-3.95618433376946</v>
       </c>
       <c r="G98">
-        <v>-11.14810103743263</v>
+        <v>-9.841749835999604</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.187458133220904</v>
       </c>
       <c r="E99">
-        <v>-41.73775375250427</v>
+        <v>-41.55576570332101</v>
       </c>
       <c r="F99">
-        <v>-3.25523292818413</v>
+        <v>-3.619927934538568</v>
       </c>
       <c r="G99">
-        <v>-11.20847545643232</v>
+        <v>-9.615116509472177</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.538832404287314</v>
       </c>
       <c r="E100">
-        <v>-45.10251635934252</v>
+        <v>-44.21515055635449</v>
       </c>
       <c r="F100">
-        <v>-3.163880019863837</v>
+        <v>-3.781499195737616</v>
       </c>
       <c r="G100">
-        <v>-11.41090538452214</v>
+        <v>-10.14827655802626</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.851988907558209</v>
       </c>
       <c r="E101">
-        <v>-47.23442682419957</v>
+        <v>-46.94877294803272</v>
       </c>
       <c r="F101">
-        <v>-3.475700628672456</v>
+        <v>-3.766902970167969</v>
       </c>
       <c r="G101">
-        <v>-11.94142030719034</v>
+        <v>-10.41601030742374</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.161961409839514</v>
       </c>
       <c r="E102">
-        <v>-49.73677665195056</v>
+        <v>-49.08468658391254</v>
       </c>
       <c r="F102">
-        <v>-3.136459735643918</v>
+        <v>-3.528388940773211</v>
       </c>
       <c r="G102">
-        <v>-11.67797371426622</v>
+        <v>-10.08712747137038</v>
       </c>
     </row>
   </sheetData>
